--- a/excel/Loanch.xlsx
+++ b/excel/Loanch.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Loanch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC66B2A3-2C28-4D74-80EB-1EE7C65DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37987F14-BCA4-4FEE-9BE6-647BE2C30AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="90203940...099922b10dbd" sheetId="32" r:id="rId3"/>
-    <sheet name="45b52ba0...0700af8e066e" sheetId="31" r:id="rId4"/>
-    <sheet name="4db6f5a8...8acf4fb9b90a" sheetId="30" r:id="rId5"/>
-    <sheet name="6836f159...155f27704bef" sheetId="29" r:id="rId6"/>
-    <sheet name="bab06fd6...b5601686ad35" sheetId="28" r:id="rId7"/>
-    <sheet name="6503e9b8...38a61e9781c1" sheetId="27" r:id="rId8"/>
-    <sheet name="edcaf7c8...13263f96f7ec" sheetId="26" r:id="rId9"/>
-    <sheet name="34060e5d...9d09fabf263e" sheetId="25" r:id="rId10"/>
-    <sheet name="8572f54e...85fb68b6201e" sheetId="24" r:id="rId11"/>
-    <sheet name="6a67a901...550919b8d681" sheetId="14" r:id="rId12"/>
+    <sheet name="dcc8ab50...7172e66514cf" sheetId="34" r:id="rId3"/>
+    <sheet name="4432e1d4...0403e0be8ebf" sheetId="33" r:id="rId4"/>
+    <sheet name="90203940...099922b10dbd" sheetId="32" r:id="rId5"/>
+    <sheet name="45b52ba0...0700af8e066e" sheetId="31" r:id="rId6"/>
+    <sheet name="4db6f5a8...8acf4fb9b90a" sheetId="30" r:id="rId7"/>
+    <sheet name="6836f159...155f27704bef" sheetId="29" r:id="rId8"/>
+    <sheet name="bab06fd6...b5601686ad35" sheetId="28" r:id="rId9"/>
+    <sheet name="6503e9b8...38a61e9781c1" sheetId="27" r:id="rId10"/>
+    <sheet name="edcaf7c8...13263f96f7ec" sheetId="26" r:id="rId11"/>
+    <sheet name="34060e5d...9d09fabf263e" sheetId="25" r:id="rId12"/>
+    <sheet name="8572f54e...85fb68b6201e" sheetId="24" r:id="rId13"/>
+    <sheet name="6a67a901...550919b8d681" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="57">
   <si>
     <t>Paskola</t>
   </si>
@@ -212,6 +214,12 @@
   </si>
   <si>
     <t>90203940...099922b10dbd</t>
+  </si>
+  <si>
+    <t>4432e1d4...0403e0be8ebf</t>
+  </si>
+  <si>
+    <t>dcc8ab50...7172e66514cf</t>
   </si>
 </sst>
 </file>
@@ -492,7 +500,63 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="52">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -835,7 +899,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE201A7-E401-4298-8793-43702E58B25B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57DB45C2-15F8-48B9-842E-E1D77BC145D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -871,6 +935,118 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA58F80-4A4F-4820-9AC1-8CCD158423E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3E6BE7-2620-4CB3-8F4E-0C17BF712D36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -947,7 +1123,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E270EAFC-C8EA-4366-981D-24AE62039ECD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A38FB8B8-F67B-4C4F-814B-9FC7D3ABA2EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1003,7 +1179,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2A7DB54-D366-4D84-B86A-9127CFF165AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE201A7-E401-4298-8793-43702E58B25B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1059,7 +1235,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6699D495-B184-490D-A9BE-00D1D918D297}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E270EAFC-C8EA-4366-981D-24AE62039ECD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1115,7 +1291,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6093F4BF-7670-408C-9E02-CC8C7C81DD2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2A7DB54-D366-4D84-B86A-9127CFF165AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1171,7 +1347,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94C725A-4ADE-42D1-9C31-B09433946415}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6699D495-B184-490D-A9BE-00D1D918D297}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1227,7 +1403,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFD5E720-E4DB-43B4-8450-81B1D8305FDB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6093F4BF-7670-408C-9E02-CC8C7C81DD2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1283,7 +1459,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA58F80-4A4F-4820-9AC1-8CCD158423E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94C725A-4ADE-42D1-9C31-B09433946415}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1339,7 +1515,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3E6BE7-2620-4CB3-8F4E-0C17BF712D36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFD5E720-E4DB-43B4-8450-81B1D8305FDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1846,7 +2022,7 @@
       </c>
       <c r="R3" s="29">
         <f>SUM(H3:H100)-U3</f>
-        <v>20.700000000000003</v>
+        <v>21.039999999999992</v>
       </c>
       <c r="S3" s="30">
         <f>Pinigai!H2</f>
@@ -1858,27 +2034,27 @@
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
-        <v>80.98</v>
+        <v>101.68</v>
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="W3" s="29">
         <f>Q3+V3+S3</f>
-        <v>20.7</v>
+        <v>21.04</v>
       </c>
       <c r="X3" s="29">
         <f>W3-Q3</f>
-        <v>0.69999999999999929</v>
+        <v>1.0399999999999991</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>3.4999999999999962E-2</v>
+        <v>5.1999999999999956E-2</v>
       </c>
       <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.10478962063789368</v>
+        <v>0.12766515612602231</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O100)</f>
@@ -2266,25 +2442,25 @@
         <f>'6836f159...155f27704bef'!B11</f>
         <v>46238</v>
       </c>
-      <c r="J9" s="6" t="str">
+      <c r="J9" s="6">
         <f>'6836f159...155f27704bef'!O3</f>
-        <v/>
-      </c>
-      <c r="K9" s="19">
+        <v>46268</v>
+      </c>
+      <c r="K9" s="19" t="str">
         <f ca="1">'6836f159...155f27704bef'!B12</f>
-        <v>-27</v>
-      </c>
-      <c r="L9" s="19">
+        <v/>
+      </c>
+      <c r="L9" s="19" t="str">
         <f ca="1">'6836f159...155f27704bef'!P3</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="M9" s="3">
         <f>'6836f159...155f27704bef'!K3</f>
-        <v>0</v>
+        <v>10.24</v>
       </c>
       <c r="N9" s="3">
         <f>'6836f159...155f27704bef'!L3</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="O9" s="3">
         <f>'6836f159...155f27704bef'!M3</f>
@@ -2293,7 +2469,7 @@
       <c r="P9" s="10"/>
       <c r="AC9" s="3" t="str">
         <f ca="1">'6836f159...155f27704bef'!Z3</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -2464,13 +2640,13 @@
         <f>'90203940...099922b10dbd'!B11</f>
         <v>46291</v>
       </c>
-      <c r="J12" s="6" t="str">
+      <c r="J12" s="6">
         <f>'90203940...099922b10dbd'!O3</f>
-        <v/>
-      </c>
-      <c r="K12" s="19">
+        <v>46290</v>
+      </c>
+      <c r="K12" s="19" t="str">
         <f ca="1">'90203940...099922b10dbd'!B12</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="L12" s="19" t="str">
         <f ca="1">'90203940...099922b10dbd'!P3</f>
@@ -2478,11 +2654,11 @@
       </c>
       <c r="M12" s="3">
         <f>'90203940...099922b10dbd'!K3</f>
-        <v>0</v>
+        <v>10.46</v>
       </c>
       <c r="N12" s="3">
         <f>'90203940...099922b10dbd'!L3</f>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O12" s="3">
         <f>'90203940...099922b10dbd'!M3</f>
@@ -2495,40 +2671,136 @@
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="3"/>
-      <c r="AC13" s="1"/>
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6">
+        <f>'4432e1d4...0403e0be8ebf'!B9</f>
+        <v>46268</v>
+      </c>
+      <c r="C13" s="26" t="str">
+        <f>'4432e1d4...0403e0be8ebf'!B1</f>
+        <v>4432e1d4...0403e0be8ebf</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f>'4432e1d4...0403e0be8ebf'!B2</f>
+        <v>Malaysia</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f>'4432e1d4...0403e0be8ebf'!B3</f>
+        <v>Tambadana</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f>'4432e1d4...0403e0be8ebf'!B8</f>
+        <v>0 m. 1 mėn. 0 d.</v>
+      </c>
+      <c r="G13" s="7">
+        <f>'4432e1d4...0403e0be8ebf'!B15</f>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="H13" s="3">
+        <f>'4432e1d4...0403e0be8ebf'!B16</f>
+        <v>10.47</v>
+      </c>
+      <c r="I13" s="6">
+        <f>'4432e1d4...0403e0be8ebf'!B11</f>
+        <v>46298</v>
+      </c>
+      <c r="J13" s="6" t="str">
+        <f>'4432e1d4...0403e0be8ebf'!O3</f>
+        <v/>
+      </c>
+      <c r="K13" s="19">
+        <f ca="1">'4432e1d4...0403e0be8ebf'!B12</f>
+        <v>5</v>
+      </c>
+      <c r="L13" s="19" t="str">
+        <f ca="1">'4432e1d4...0403e0be8ebf'!P3</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
+        <f>'4432e1d4...0403e0be8ebf'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <f>'4432e1d4...0403e0be8ebf'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <f>'4432e1d4...0403e0be8ebf'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="AC13" s="3" t="str">
+        <f ca="1">'4432e1d4...0403e0be8ebf'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="3"/>
-      <c r="AC14" s="1"/>
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6">
+        <f>'dcc8ab50...7172e66514cf'!B9</f>
+        <v>46291</v>
+      </c>
+      <c r="C14" s="26" t="str">
+        <f>'dcc8ab50...7172e66514cf'!B1</f>
+        <v>dcc8ab50...7172e66514cf</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f>'dcc8ab50...7172e66514cf'!B2</f>
+        <v>Malaysia</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f>'dcc8ab50...7172e66514cf'!B3</f>
+        <v>Tambadana</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f>'dcc8ab50...7172e66514cf'!B8</f>
+        <v>0 m. 1 mėn. 0 d.</v>
+      </c>
+      <c r="G14" s="7">
+        <f>'dcc8ab50...7172e66514cf'!B15</f>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="H14" s="3">
+        <f>'dcc8ab50...7172e66514cf'!B16</f>
+        <v>10.57</v>
+      </c>
+      <c r="I14" s="6">
+        <f>'dcc8ab50...7172e66514cf'!B11</f>
+        <v>46321</v>
+      </c>
+      <c r="J14" s="6" t="str">
+        <f>'dcc8ab50...7172e66514cf'!O3</f>
+        <v/>
+      </c>
+      <c r="K14" s="19">
+        <f ca="1">'dcc8ab50...7172e66514cf'!B12</f>
+        <v>28</v>
+      </c>
+      <c r="L14" s="19" t="str">
+        <f ca="1">'dcc8ab50...7172e66514cf'!P3</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
+        <f>'4432e1d4...0403e0be8ebf'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <f>'dcc8ab50...7172e66514cf'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <f>'dcc8ab50...7172e66514cf'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="AC14" s="3" t="str">
+        <f ca="1">'dcc8ab50...7172e66514cf'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -2774,20 +3046,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
-    <cfRule type="expression" dxfId="43" priority="15">
+    <cfRule type="expression" dxfId="51" priority="17">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="16">
+    <cfRule type="expression" dxfId="50" priority="18">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="41" priority="2">
+    <cfRule type="expression" dxfId="49" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC5:AC12">
-    <cfRule type="expression" dxfId="40" priority="1">
+  <conditionalFormatting sqref="AC5:AC14">
+    <cfRule type="expression" dxfId="48" priority="1">
       <formula>$AC5="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2801,7 +3073,9 @@
     <hyperlink ref="C9" location="'6836f159...155f27704bef'!A1" display="'6836f159...155f27704bef'!A1" xr:uid="{6FBE713B-C5C1-4487-AEB0-76FB8384D359}"/>
     <hyperlink ref="C10" location="'4db6f5a8...8acf4fb9b90a'!A1" display="'4db6f5a8...8acf4fb9b90a'!A1" xr:uid="{51C54BD2-6758-450A-BD35-5AEE8C98C71A}"/>
     <hyperlink ref="C11" location="'45b52ba0...0700af8e066e'!A1" display="'45b52ba0...0700af8e066e'!A1" xr:uid="{99FD08BF-C515-4DD4-9F3D-763A30898E51}"/>
-    <hyperlink ref="C12" location="'45b52ba0...0700af8e066e'!A1" display="'45b52ba0...0700af8e066e'!A1" xr:uid="{C5788568-CC7C-49A1-B48C-5CA88B7536B0}"/>
+    <hyperlink ref="C12" location="'90203940...099922b10dbd'!A1" display="'90203940...099922b10dbd'!A1" xr:uid="{C5788568-CC7C-49A1-B48C-5CA88B7536B0}"/>
+    <hyperlink ref="C13" location="'4432e1d4...0403e0be8ebf'!A1" display="'4432e1d4...0403e0be8ebf'!A1" xr:uid="{2CA73251-4455-4A53-8530-E3835D87BB68}"/>
+    <hyperlink ref="C14" location="dcc8ab50...7172e66514cf!A1" display="dcc8ab50...7172e66514cf!A1" xr:uid="{9C68683D-082E-42DC-93EC-1CD02ECFEE9A}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="50" orientation="landscape" r:id="rId1"/>
@@ -2809,7 +3083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D73BEB5-FF23-4AB2-910E-BFC1E1552858}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFD3710-89A2-4F7D-A324-B3CED3BB72D8}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -2836,7 +3110,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
@@ -2927,20 +3201,20 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46181</v>
+        <v>46208</v>
       </c>
       <c r="E3" s="6">
-        <v>46177</v>
+        <v>46208</v>
       </c>
       <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>10.029999999999999</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="H3" s="3">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -2948,11 +3222,11 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.029999999999999</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -2960,11 +3234,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.1435224711894989</v>
+        <v>0.14042803645133972</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46177</v>
+        <v>46208</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -2972,16 +3246,16 @@
       </c>
       <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.029999999999999</v>
+        <v>-10.130000000000001</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -3007,11 +3281,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46177</v>
+        <v>46208</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.129999999999999</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3112,7 +3386,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -3138,7 +3412,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -3164,7 +3438,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46181</v>
+        <v>46208</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -3295,7 +3569,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.029999999999999</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -4052,11 +4326,1297 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.029999999999999</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.1</v>
+        <v>0.11</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="19" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="16" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894C5DD5-26F0-4BD8-A02A-9EA73D3EF2C5}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46155</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46185</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>30</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.12</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.14999164938926698</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46185</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>30</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46154</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.050000000000001</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46185</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 0 mėn. 1 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46154</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46124</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46155</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.050000000000001</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -4094,7 +5654,1293 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D73BEB5-FF23-4AB2-910E-BFC1E1552858}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46181</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46177</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>-4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.029999999999999</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.1</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.1435224711894989</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46177</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>-4</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46150</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.029999999999999</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46177</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.129999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 1 mėn. 0 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46181</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.029999999999999</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="8" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E60DD-D268-4B5D-B986-F933A571227C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5357,20 +8203,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5380,7 +8226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6642,20 +9488,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8122,14 +10968,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46265</v>
+        <v>46293</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>20.7</v>
+        <v>21.04</v>
       </c>
     </row>
   </sheetData>
@@ -8138,7 +10984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBD262D-AFFA-4485-9906-FB8E3EB69FC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB57FB50-E87A-4757-B521-5968F523A6F5}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8162,7 +11008,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
@@ -8284,11 +11130,11 @@
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46261</v>
+        <v>46291</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.46</v>
+        <v>-10.57</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -8393,7 +11239,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 30 d.</v>
+        <v>0 m. 1 mėn. 0 d.</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="6"/>
@@ -8419,7 +11265,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46261</v>
+        <v>46291</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -8445,7 +11291,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46261</v>
+        <v>46291</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -8471,7 +11317,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46291</v>
+        <v>46321</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -8498,7 +11344,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -8602,7 +11448,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -9378,20 +12224,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="44" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9402,6 +12248,2556 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DB26AD-2701-43EA-A856-E4E6EAF3884D}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="19" t="str">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46268</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.47</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 1 mėn. 0 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46268</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46268</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46298</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>5</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.47</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="43" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="41" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="40" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBD262D-AFFA-4485-9906-FB8E3EB69FC9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46291</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46290</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>-1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.46</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.46</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.11</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.14073022007942199</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46290</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>-1</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46261</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.46</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46290</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 0 mėn. 30 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46261</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46261</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46291</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.46</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.46</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="39" priority="2">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="3">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="37" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="36" priority="5">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D413F8-1679-4095-AA32-963FC106BE84}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10650,1292 +16046,6 @@
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
         <v>0.12</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="39" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="37" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="36" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355B2BCE-B3A8-4634-BB20-53D0C8F481D1}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46231</v>
-      </c>
-      <c r="F3" s="19">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-8</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.26</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>10.26</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.08</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.13753321766853335</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46231</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-8</v>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46209</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-10.26</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="19" t="str">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="10"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46231</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="19" t="str">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="10"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="10"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 30 d.</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="10"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46209</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46209</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46239</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="19" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="18"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="18"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10.26</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="11"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="11"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="11"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="11"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="11"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="11"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="11"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="11"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="11"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="11"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="11"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="11"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="11"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="11"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="11"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="11"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="11"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="11"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="11"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="11"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="11"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="11"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="11"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="11"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="11"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="11"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="11"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="11"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="11"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="11"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="11"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="11"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="11"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="11"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="11"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="10"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>10.26</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.08</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -11973,10 +16083,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DFB9D0-FFDA-4CA0-9F51-BFCBF06C03C2}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355B2BCE-B3A8-4634-BB20-53D0C8F481D1}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12001,7 +16111,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
@@ -12092,57 +16202,65 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46238</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="19" t="str">
+        <v>46239</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46231</v>
+      </c>
+      <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>-8</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.26</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.13753321766853335</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2">
+        <v>46231</v>
+      </c>
+      <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v>27</v>
-      </c>
-      <c r="Q3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>-8</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.24</v>
+        <v>-10.26</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -12164,11 +16282,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46231</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -12269,7 +16387,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -12295,7 +16413,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -12321,7 +16439,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -12346,9 +16464,9 @@
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="19" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>-27</v>
+        <v/>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -12452,7 +16570,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.24</v>
+        <v>10.26</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -13209,11 +17327,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -13251,8 +17369,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E38648-85FB-451A-8C48-F23050BE99C9}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DFB9D0-FFDA-4CA0-9F51-BFCBF06C03C2}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -13279,7 +17397,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
@@ -13370,20 +17488,20 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46215</v>
+        <v>46238</v>
       </c>
       <c r="E3" s="6">
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-6</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3">
-        <v>10.17</v>
+        <v>10.24</v>
       </c>
       <c r="H3" s="3">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -13391,11 +17509,11 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.17</v>
+        <v>10.24</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -13403,11 +17521,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14338709712028502</v>
+        <v>0.14468039870262145</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -13415,16 +17533,16 @@
       </c>
       <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-6</v>
+        <v>30</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46185</v>
+        <v>46208</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.17</v>
+        <v>-10.24</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -13450,11 +17568,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46209</v>
+        <v>46268</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.26</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -13529,7 +17647,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 1 mėn. 0 d.</v>
+        <v>0 m. 0 mėn. 30 d.</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="6"/>
@@ -13555,7 +17673,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46185</v>
+        <v>46208</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -13581,7 +17699,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46185</v>
+        <v>46208</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -13607,7 +17725,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46215</v>
+        <v>46238</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -13738,7 +17856,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.17</v>
+        <v>10.24</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -14495,11 +18613,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.17</v>
+        <v>10.24</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -14537,8 +18655,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFD3710-89A2-4F7D-A324-B3CED3BB72D8}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E38648-85FB-451A-8C48-F23050BE99C9}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -14565,7 +18683,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="34" t="s">
         <v>2</v>
@@ -14656,20 +18774,20 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="E3" s="6">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G3" s="3">
-        <v>10.130000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="H3" s="3">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -14677,11 +18795,11 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.130000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -14689,11 +18807,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14042803645133972</v>
+        <v>0.14338709712028502</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -14701,16 +18819,16 @@
       </c>
       <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.130000000000001</v>
+        <v>-10.17</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -14736,11 +18854,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.24</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -14841,7 +18959,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -14867,7 +18985,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46178</v>
+        <v>46185</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -14893,7 +19011,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -15024,7 +19142,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.130000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -15781,11 +19899,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.130000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -15821,1290 +19939,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894C5DD5-26F0-4BD8-A02A-9EA73D3EF2C5}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="36"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46155</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46185</v>
-      </c>
-      <c r="F3" s="19">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>30</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.12</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.12</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14999164938926698</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46185</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>30</v>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46154</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-10.050000000000001</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="19" t="str">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="10"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46185</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="19" t="str">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="10"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="10"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 1 d.</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="10"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46154</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46124</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="19" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="18"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="18"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="11"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="11"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="11"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="11"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="11"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="11"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="11"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="11"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="11"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="11"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="11"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="11"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="11"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="11"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="11"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="11"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="11"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="11"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="11"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="11"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="11"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="11"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="11"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="11"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="11"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="11"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="11"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="11"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="11"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="11"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="11"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="11"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="11"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="11"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="11"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="10"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.12</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="19" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="16" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>